--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>TAREAS</t>
   </si>
@@ -66,13 +66,25 @@
   </si>
   <si>
     <t>Dino JUMP</t>
+  </si>
+  <si>
+    <t>cactus MOVE</t>
+  </si>
+  <si>
+    <t>Add details</t>
+  </si>
+  <si>
+    <t>DON'T JUMP</t>
+  </si>
+  <si>
+    <t>NO MOVE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +117,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -158,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -174,6 +192,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -223,8 +243,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:D10" totalsRowShown="0">
-  <autoFilter ref="A1:D10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:D17" totalsRowShown="0">
+  <autoFilter ref="A1:D17"/>
   <tableColumns count="4">
     <tableColumn id="1" name="TAREAS" dataDxfId="1"/>
     <tableColumn id="2" name="CHECKED"/>
@@ -498,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
@@ -556,36 +576,85 @@
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>TAREAS</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Add details</t>
-  </si>
-  <si>
-    <t>DON'T JUMP</t>
   </si>
   <si>
     <t>NO MOVE</t>
@@ -601,9 +598,8 @@
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -619,7 +615,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="4"/>
     </row>

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>TAREAS</t>
   </si>
@@ -598,7 +598,9 @@
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C10" s="14"/>
       <c r="D10" s="4"/>
     </row>

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>TAREAS</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>NO MOVE</t>
+  </si>
+  <si>
+    <t>GAME OVER</t>
+  </si>
+  <si>
+    <t>LETTERS</t>
+  </si>
+  <si>
+    <t>ANIMATION</t>
   </si>
 </sst>
 </file>
@@ -123,7 +132,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,6 +166,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -173,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -191,6 +206,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,7 +592,9 @@
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -602,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -622,8 +640,13 @@
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="D13" s="14"/>
+      <c r="A13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="15"/>
       <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>TAREAS</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>GAME OVER</t>
-  </si>
-  <si>
-    <t>LETTERS</t>
   </si>
   <si>
     <t>ANIMATION</t>
@@ -132,7 +129,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,12 +166,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -188,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -206,7 +197,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -643,10 +633,11 @@
       <c r="A13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="15"/>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
       <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>TAREAS</t>
   </si>
@@ -74,13 +74,22 @@
     <t>Add details</t>
   </si>
   <si>
-    <t>NO MOVE</t>
-  </si>
-  <si>
     <t>GAME OVER</t>
   </si>
   <si>
     <t>ANIMATION</t>
+  </si>
+  <si>
+    <t>CLOUDS</t>
+  </si>
+  <si>
+    <t>COINS</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>CRASH</t>
   </si>
 </sst>
 </file>
@@ -570,20 +579,26 @@
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -591,7 +606,9 @@
       <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -624,14 +641,16 @@
       <c r="A12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4"/>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -641,12 +660,20 @@
       <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
     </row>

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>TAREAS</t>
   </si>
@@ -673,7 +673,10 @@
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
     </row>

--- a/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
+++ b/DINO_LLMM_U2_PF1/Tareas Game Project.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>TAREAS</t>
   </si>
@@ -77,19 +77,19 @@
     <t>GAME OVER</t>
   </si>
   <si>
-    <t>ANIMATION</t>
-  </si>
-  <si>
-    <t>CLOUDS</t>
-  </si>
-  <si>
     <t>COINS</t>
   </si>
   <si>
-    <t>ADD</t>
-  </si>
-  <si>
     <t>CRASH</t>
+  </si>
+  <si>
+    <t>DETECTAR</t>
+  </si>
+  <si>
+    <t>RESET</t>
+  </si>
+  <si>
+    <t>BTN</t>
   </si>
 </sst>
 </file>
@@ -138,7 +138,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,6 +175,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -188,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -206,6 +212,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,19 +604,21 @@
       <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="14"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="4"/>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -661,17 +670,17 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -681,7 +690,12 @@
       <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
     </row>
